--- a/TIMES-NZ/v303/VT_TIMESNZ_ELC.xlsx
+++ b/TIMES-NZ/v303/VT_TIMESNZ_ELC.xlsx
@@ -4643,7 +4643,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>18337.0</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>18337.0</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -10035,7 +10035,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
